--- a/demo/fixtures/reporteExogena2025_demo.xlsx
+++ b/demo/fixtures/reporteExogena2025_demo.xlsx
@@ -499,6 +499,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -513,6 +514,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -628,7 +630,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1019072850</t>
+          <t>123444</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -666,7 +668,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1019072850</t>
+          <t>123444</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -704,7 +706,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1019072850</t>
+          <t>123444</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -742,7 +744,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1019072850</t>
+          <t>123444</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -780,7 +782,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1019072850</t>
+          <t>123444</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -818,7 +820,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1019072850</t>
+          <t>123444</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -856,7 +858,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1019072850</t>
+          <t>123444</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -894,7 +896,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1019072850</t>
+          <t>123444</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -932,7 +934,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1019072850</t>
+          <t>123444</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -970,7 +972,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1019072850</t>
+          <t>123444</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1008,7 +1010,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1019072850</t>
+          <t>123444</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1046,7 +1048,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1019072850</t>
+          <t>123444</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1019072850</t>
+          <t>123444</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1122,7 +1124,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1019072850</t>
+          <t>123444</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
